--- a/directory/engine/assets/xlsx/self_links.xlsx
+++ b/directory/engine/assets/xlsx/self_links.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>全球最大的综合搜索引擎</t>
+          <t>全球索引量最大的多语综合搜索，学术、地图、翻译等延伸服务齐全</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>微软综合搜索引擎</t>
+          <t>微软旗下综合搜索，深度集成 Windows 与 Copilot AI 智能应答</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>中文综合搜索引擎</t>
+          <t>中文网页与语义理解见长，贴吧、知道、百科构成内容生态闭环</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>阿里巴巴旗下购物搜索</t>
+          <t>电商商品与店铺检索，支持销量、价格、信用筛选与直播带货</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>自营电商购物平台</t>
+          <t>自营与品牌电商检索，以物流时效与正品保障为特色的购物搜索</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -857,7 +857,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>拼团购物平台</t>
+          <t>低价拼团模式下的商品搜索，下沉市场供给与农货丰富</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>中文问答与知识社区</t>
+          <t>高质量中文问答社区，专业答主长文与观点检索入口</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -971,7 +971,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>自由开放的网络百科全书</t>
+          <t>非营利的协作百科，引用可追溯、跨语言词条互链</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>微信公众号与文章搜索</t>
+          <t>检索公众号文章、视频号与朋友圈内容，封闭生态内搜索</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>字节系通用搜索</t>
+          <t>基于字节推荐算法的通用搜索，信息流与热点聚合</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>年轻人文化视频社区</t>
+          <t>ACG 与 UP 主视频检索，弹幕文化与番剧社区入口</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>短视频内容搜索</t>
+          <t>短视频内容搜索，按热点与挑战标签分发与发现</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>全球代码托管与搜索</t>
+          <t>代码仓库与开源项目检索，支持 Issue、PR 与代码全文搜索</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>程序员问答社区</t>
+          <t>编程报错与技术方案问答检索，按投票质量排序</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>开发者技术社区</t>
+          <t>前端、客户端与后端技术文章、教程与专栏检索</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>地图与位置搜索</t>
+          <t>POI 地点、路线与实时路况检索，含打车与周边服务</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>词典与翻译</t>
+          <t>中英及多语词典与整句翻译，支持文档与网页翻译</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>音乐搜索与收听</t>
+          <t>歌曲、歌单与歌词检索推荐，以乐评社区为特色</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>

--- a/directory/engine/assets/xlsx/self_links.xlsx
+++ b/directory/engine/assets/xlsx/self_links.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22680" windowHeight="10410" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="14340" windowHeight="9780" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" state="visible" r:id="rId1"/>
@@ -622,55 +622,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB68"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="4.125" customWidth="1" min="1" max="1"/>
@@ -1056,54 +1056,54 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>dir_path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>cat_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>cat_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>card_layout</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>card_title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>card_desc</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>card_media</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>card_tags</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>card_id</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>card_order</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>link_1_id</t>
-        </is>
-      </c>
       <c r="L1" t="inlineStr">
         <is>
           <t>link_1_name</t>
@@ -1116,337 +1116,92 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>link_1_desc</t>
+          <t>link_2_name</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>link_1_media</t>
+          <t>link_2_url</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>link_1_enabled</t>
+          <t>link_3_name</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>link_2_id</t>
+          <t>link_3_url</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>link_2_name</t>
+          <t>link_4_name</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>link_2_url</t>
+          <t>link_4_url</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>link_2_desc</t>
+          <t>link_5_name</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>link_2_media</t>
+          <t>link_5_url</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>link_2_enabled</t>
+          <t>link_6_name</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>link_3_id</t>
+          <t>link_6_url</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>link_3_name</t>
+          <t>link_7_name</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>link_3_url</t>
+          <t>link_7_url</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>link_3_desc</t>
+          <t>link_8_name</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>link_3_media</t>
+          <t>link_8_url</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>link_3_enabled</t>
+          <t>link_9_name</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>link_4_id</t>
+          <t>link_9_url</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>link_4_name</t>
+          <t>link_10_name</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>link_4_url</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>link_4_desc</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>link_4_media</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>link_4_enabled</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>link_5_id</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>link_5_name</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>link_5_url</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>link_5_desc</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>link_5_media</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>link_5_enabled</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>link_6_id</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>link_6_name</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>link_6_url</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>link_6_desc</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>link_6_media</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>link_6_enabled</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>link_7_id</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>link_7_name</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>link_7_url</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>link_7_desc</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>link_7_media</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>link_7_enabled</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>link_8_id</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>link_8_name</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>link_8_url</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>link_8_desc</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>link_8_media</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>link_8_enabled</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>link_9_id</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>link_9_name</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>link_9_url</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>link_9_desc</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>link_9_media</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>link_9_enabled</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>link_10_id</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>link_10_name</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
           <t>link_10_url</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>link_10_desc</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>link_10_media</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>link_10_enabled</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>source_1_name</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>source_1_url</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>source_2_name</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>source_2_url</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>source_3_name</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>source_3_url</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>source_4_name</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>source_4_url</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>source_5_name</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>source_5_url</t>
         </is>
       </c>
     </row>
@@ -1454,25 +1209,25 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Google 搜索</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>谷歌搜索引擎，全球索引量最大的多语综合搜索，学术、地图、翻译等延伸服务齐全</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1485,16 +1240,6 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>https://www.google.com</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="BT2" s="1" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/%E8%B0%B7%E6%AD%8C%E6%90%9C%E7%B4%A2%E5%BC%95%E6%93%8E</t>
         </is>
       </c>
     </row>
@@ -1502,25 +1247,25 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>必应 Bing</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>微软旗下综合搜索，深度集成 Windows 与 Copilot AI 智能应答</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1533,16 +1278,6 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://www.bing.com</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="BT3" s="1" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/%E5%BF%85%E5%BA%94%20Bing</t>
         </is>
       </c>
     </row>
@@ -1550,25 +1285,25 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>百度搜索</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>中文网页与语义理解见长，贴吧、知道、百科构成内容生态闭环</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1581,16 +1316,6 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>https://www.baidu.com</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>百度百科</t>
-        </is>
-      </c>
-      <c r="BT4" s="1" t="inlineStr">
-        <is>
-          <t>https://baike.baidu.com/item/%E7%99%BE%E5%BA%A6%E6%90%9C%E7%B4%A2</t>
         </is>
       </c>
     </row>
@@ -1598,25 +1323,25 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>购物</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>淘宝</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>电商商品与店铺检索，支持销量、价格、信用筛选与直播带货</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1636,25 +1361,25 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>购物</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>京东</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>自营与品牌电商检索，以物流时效与正品保障为特色的购物搜索</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1674,25 +1399,25 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>购物</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>拼多多</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>低价拼团模式下的商品搜索，下沉市场供给与农货丰富</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1712,25 +1437,25 @@
       <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>社区知识</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>知乎</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>高质量中文问答社区，专业答主长文与观点检索入口</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1750,25 +1475,25 @@
       <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>社区知识</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>维基百科</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>非营利的协作百科，引用可追溯、跨语言词条互链</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1788,25 +1513,25 @@
       <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>社区知识</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>微信搜一搜</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>检索公众号文章、视频号与朋友圈内容，封闭生态内搜索</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1826,25 +1551,25 @@
       <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>社区知识</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>头条搜索</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>基于字节推荐算法的通用搜索，信息流与热点聚合</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1864,25 +1589,25 @@
       <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>视频</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>哔哩哔哩</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ACG 与 UP 主视频检索，弹幕文化与番剧社区入口</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1902,25 +1627,25 @@
       <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>视频</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>抖音</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>短视频内容搜索，按热点与挑战标签分发与发现</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1940,25 +1665,25 @@
       <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>开发</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>代码仓库与开源项目检索，支持 Issue、PR 与代码全文搜索</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -1978,25 +1703,25 @@
       <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>开发</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Stack Overflow</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>编程报错与技术方案问答检索，按投票质量排序</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -2016,25 +1741,25 @@
       <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>开发</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>掘金</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>前端、客户端与后端技术文章、教程与专栏检索</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -2054,25 +1779,25 @@
       <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>高德地图</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>POI 地点、路线与实时路况检索，含打车与周边服务</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -2092,25 +1817,25 @@
       <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>有道翻译</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>中英及多语词典与整句翻译，支持文档与网页翻译</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -2130,25 +1855,25 @@
       <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>网易云音乐</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>歌曲、歌单与歌词检索推荐，以乐评社区为特色</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>搜索引擎,聚合搜索</t>
         </is>
@@ -2168,20 +1893,20 @@
       <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>数据库</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>在线读报</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>九星时代报刊在线系统包含了综合报、晨报、日报、晚报、都市报、经济报、生活报、法制报、农业报、军事报、体育报、青少年、保健报和其他14大类的报纸资源，可以充分的满足不同用户的阅读需求。 使用指南 缩放功能 单击报纸任何一点，便可将报纸整版放大，同理单击放大后的报纸任意一处，即可缩小。同时也可用右侧操作项进行放大缩小。拖动功能 ：当报纸放大后，手指可随意拖动整版报纸，将超出显示区位置的报纸托动至显示区内。翻页功能：点住报纸画面，向左或向右横向滑动，即可将报纸翻页。</t>
         </is>
@@ -2196,14 +1921,9 @@
           <t>http://202.106.125.196</t>
         </is>
       </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>中国政协网 - 信息资料 - 国家图书馆政协委员服务平台</t>
-        </is>
-      </c>
-      <c r="BT20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cppcc.gov.cn/</t>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>http://202.106.125.196</t>
         </is>
       </c>
     </row>
@@ -2211,15 +1931,15 @@
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>数据库</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>国务院政策文件库</t>
         </is>
@@ -2234,14 +1954,9 @@
           <t>https://sousuo.www.gov.cn/zcwjk/</t>
         </is>
       </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>中国政协网 - 信息资料</t>
-        </is>
-      </c>
-      <c r="BT21" s="1" t="inlineStr">
-        <is>
-          <t>https://www.cppcc.gov.cn/</t>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://sousuo.www.gov.cn/zcwjk/</t>
         </is>
       </c>
     </row>
@@ -2249,25 +1964,25 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>DuckDuckGo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>隐私搜索引擎，不收集用户信息、无广告</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>搜索引擎,隐私</t>
         </is>
@@ -2280,16 +1995,6 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>https://duckduckgo.com/</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2297,25 +2002,25 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Yandex</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>俄罗斯主流综合搜索引擎</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>搜索引擎</t>
         </is>
@@ -2328,16 +2033,6 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>https://yandex.com/</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2345,25 +2040,25 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Qwant</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>法国搜索引擎，注重隐私保护</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>搜索引擎,隐私</t>
         </is>
@@ -2376,16 +2071,6 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>https://www.qwant.com/</t>
-        </is>
-      </c>
-      <c r="BS24" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT24" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2393,25 +2078,25 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>对话式 AI 搜索引擎，直接给出带引用的答案</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>搜索引擎,AI搜索</t>
         </is>
@@ -2424,16 +2109,6 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>https://www.perplexity.ai/</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT25" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2441,25 +2116,25 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>You.com</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>AI 搜索引擎，整合多模型结果并支持对话</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>搜索引擎,AI搜索</t>
         </is>
@@ -2472,16 +2147,6 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>https://you.com/</t>
-        </is>
-      </c>
-      <c r="BS26" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT26" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2489,25 +2154,25 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>综合搜索</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Felo</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>免费 AI 智能搜索引擎，支持多语问答</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>搜索引擎,AI搜索</t>
         </is>
@@ -2520,16 +2185,6 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>https://felo.ai/search</t>
-        </is>
-      </c>
-      <c r="BS27" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT27" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2537,25 +2192,25 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>社区知识</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>知乎搜索</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>搜索知乎站内的问答与文章</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>搜索引擎,社区</t>
         </is>
@@ -2568,16 +2223,6 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>https://zhihu.sogou.com/</t>
-        </is>
-      </c>
-      <c r="BS28" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT28" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2585,25 +2230,25 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>社区知识</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>WikiHow</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>综合技能与万事指南搜索站</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>知识,指南</t>
         </is>
@@ -2616,16 +2261,6 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>https://zh.wikihow.com/</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT29" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2633,25 +2268,25 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>开发</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>开发者搜索</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>百度面向开发者的垂直搜索引擎</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>搜索引擎,开发</t>
         </is>
@@ -2664,16 +2299,6 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>https://kaifa.baidu.com/</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT30" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2681,25 +2306,25 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>TinEye</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>以图搜图的反向图片检索搜索引擎</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>以图搜图,工具</t>
         </is>
@@ -2712,16 +2337,6 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>https://www.tineye.com</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT31" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2729,25 +2344,25 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>网站历史快照</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Internet Archive 查看网站历史存档快照</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>工具,归档</t>
         </is>
@@ -2760,16 +2375,6 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>https://archive.org/</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT32" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2777,25 +2382,25 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>SimilarWeb</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>查看并分析任意网站的流量与排名</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>工具,分析</t>
         </is>
@@ -2808,16 +2413,6 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>https://www.similarweb.com/zh/</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT33" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2825,25 +2420,25 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>相似网站</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>寻找功能相似的网站推荐</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>工具,发现</t>
         </is>
@@ -2856,16 +2451,6 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>https://www.similarsitesearch.com/</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2873,25 +2458,25 @@
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Windy</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>可视化天气数据与气象预报查询</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>工具,天气</t>
         </is>
@@ -2904,16 +2489,6 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>https://www.windy.com/</t>
-        </is>
-      </c>
-      <c r="BS35" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT35" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2921,25 +2496,25 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Google 图书</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>检索正规出版书籍、杂志、报纸的摘要</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>图书,搜索</t>
         </is>
@@ -2952,16 +2527,6 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>https://books.google.com/</t>
-        </is>
-      </c>
-      <c r="BS36" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT36" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -2969,25 +2534,25 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>CC Search</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>检索可免费使用的无版权图片资源</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>图片,素材</t>
         </is>
@@ -3000,16 +2565,6 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>https://ccsearch.creativecommons.org/</t>
-        </is>
-      </c>
-      <c r="BS37" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT37" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3017,25 +2572,25 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Pexels</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>高质量免费图片与视频素材库</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>图片,素材</t>
         </is>
@@ -3048,16 +2603,6 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>https://www.pexels.com/</t>
-        </is>
-      </c>
-      <c r="BS38" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT38" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3065,25 +2610,25 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Unsplash</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>免费高清图片素材社区</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>图片,素材</t>
         </is>
@@ -3096,16 +2641,6 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>https://unsplash.com/</t>
-        </is>
-      </c>
-      <c r="BS39" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT39" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3113,25 +2648,25 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>LibreStock</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>检索多家图库的优质高清图片</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>图片,素材</t>
         </is>
@@ -3144,16 +2679,6 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>https://librestock.com/</t>
-        </is>
-      </c>
-      <c r="BS40" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT40" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3161,25 +2686,25 @@
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Iconfinder</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>查找 logo 等矢量图标素材</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>图标,素材</t>
         </is>
@@ -3192,16 +2717,6 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>https://www.iconfinder.com/</t>
-        </is>
-      </c>
-      <c r="BS41" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT41" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3209,25 +2724,25 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>FindIcons</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>优秀图标素材库检索</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>图标,素材</t>
         </is>
@@ -3240,16 +2755,6 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>https://findicons.com/</t>
-        </is>
-      </c>
-      <c r="BS42" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT42" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3257,25 +2762,25 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>谷歌学术</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Google 提供的免费学术文章搜索</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>学术,搜索</t>
         </is>
@@ -3288,16 +2793,6 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>https://scholar.google.com/</t>
-        </is>
-      </c>
-      <c r="BS43" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT43" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3305,25 +2800,25 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>百度学术</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>百度学术信息搜索引擎</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>学术,搜索</t>
         </is>
@@ -3336,16 +2831,6 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>https://xueshu.baidu.com/</t>
-        </is>
-      </c>
-      <c r="BS44" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT44" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3353,25 +2838,25 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>中国知网</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>精品论文与学术资源检索平台</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>学术,数据库</t>
         </is>
@@ -3384,16 +2869,6 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>https://www.cnki.net/</t>
-        </is>
-      </c>
-      <c r="BS45" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT45" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3401,25 +2876,25 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Semantic Scholar</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>免费学术搜索引擎（期刊/会议资料）</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>学术,搜索</t>
         </is>
@@ -3432,16 +2907,6 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>https://www.semanticscholar.org/</t>
-        </is>
-      </c>
-      <c r="BS46" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT46" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3449,25 +2914,25 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>多学科开放学术资源集成检索</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>学术,搜索</t>
         </is>
@@ -3480,16 +2945,6 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>https://www.base-search.net/</t>
-        </is>
-      </c>
-      <c r="BS47" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT47" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3497,25 +2952,25 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>arXiv</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>预印本学术论文检索库</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>学术,论文</t>
         </is>
@@ -3528,16 +2983,6 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>https://arxiv.org/</t>
-        </is>
-      </c>
-      <c r="BS48" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT48" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3545,25 +2990,25 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>PubMed</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>生物医学论文免费检索数据库</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>学术,医学</t>
         </is>
@@ -3576,16 +3021,6 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>https://pubmed.ncbi.nlm.nih.gov/</t>
-        </is>
-      </c>
-      <c r="BS49" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT49" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3593,25 +3028,25 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>万方数据</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>大型学术文献与学位论文数据库</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>学术,数据库</t>
         </is>
@@ -3624,16 +3059,6 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>https://www.wanfangdata.com.cn/</t>
-        </is>
-      </c>
-      <c r="BS50" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT50" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3641,25 +3066,25 @@
       <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>DOAJ</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>开放获取期刊目录检索</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>学术,期刊</t>
         </is>
@@ -3672,16 +3097,6 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>https://doaj.org/</t>
-        </is>
-      </c>
-      <c r="BS51" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT51" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3689,25 +3104,25 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>AMiner</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>科技情报大数据挖掘与检索平台</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>学术,搜索</t>
         </is>
@@ -3720,16 +3135,6 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>https://www.aminer.cn/</t>
-        </is>
-      </c>
-      <c r="BS52" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT52" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3737,25 +3142,25 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>CiteSeerX</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>计算机与信息科学搜索引擎</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>学术,搜索</t>
         </is>
@@ -3768,16 +3173,6 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>https://citeseer.ist.psu.edu/</t>
-        </is>
-      </c>
-      <c r="BS53" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT53" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3785,25 +3180,25 @@
       <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>学术搜索</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>ScienceDirect</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>科技文献与期刊检索平台</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>学术,数据库</t>
         </is>
@@ -3816,16 +3211,6 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>https://www.sciencedirect.com/</t>
-        </is>
-      </c>
-      <c r="BS54" t="inlineStr">
-        <is>
-          <t>菜鸟工具·搜索引擎大全</t>
-        </is>
-      </c>
-      <c r="BT54" t="inlineStr">
-        <is>
-          <t>https://www.jyshare.com/</t>
         </is>
       </c>
     </row>
@@ -3833,25 +3218,25 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>ChatGPT</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>OpenAI 推出的通用对话式 AI 助手,支持问答、写作、编程与数据分析</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>AI对话,人工智能助手</t>
         </is>
@@ -3871,25 +3256,25 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>深度求索推出的国产大模型对话助手,推理与代码能力突出</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>AI对话,国产大模型</t>
         </is>
@@ -3909,25 +3294,25 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Claude</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Anthropic 出品的对话 AI,长文本处理与安全对齐表现出色</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>AI对话,人工智能助手</t>
         </is>
@@ -3947,25 +3332,25 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Gemini</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Google 多模态对话 AI,整合搜索与生产力工具</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>AI对话,多模态</t>
         </is>
@@ -3985,25 +3370,25 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>文心一言</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>百度文心大模型对话助手(现文小言),中文理解与创作能力强</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>AI对话,国产大模型</t>
         </is>
@@ -4023,25 +3408,25 @@
       <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Kimi</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>月之暗面长上下文对话助手,擅长长文档阅读与总结</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>AI对话,长文本</t>
         </is>
@@ -4061,25 +3446,25 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>豆包</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>字节跳动推出的综合对话 AI 助手,覆盖问答与创作</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>AI对话,国产大模型</t>
         </is>
@@ -4099,25 +3484,25 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>通义千问</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>阿里通义系列大模型对话助手,支持多模态与 Agent</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>AI对话,国产大模型</t>
         </is>
@@ -4137,25 +3522,25 @@
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>智谱清言</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>智谱 AI 的 GLM 大模型对话助手,推理与工具调用均衡</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>AI对话,国产大模型</t>
         </is>
@@ -4175,25 +3560,25 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Copilot</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>微软 AI 对话助手,深度集成 Windows 与 Office 生产力</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>AI对话,生产力</t>
         </is>
@@ -4213,25 +3598,25 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Meta AI</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Meta 推出的通用对话 AI 助手,跨社交平台可用</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>AI对话,人工智能助手</t>
         </is>
@@ -4251,25 +3636,25 @@
       <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Grok</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>xAI 推出的对话 AI,接入 X 平台实时信息</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>AI对话,实时</t>
         </is>
@@ -4289,25 +3674,25 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Poe</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Quora 聚合多模型的对话平台,可一键切换不同 AI</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>AI对话,聚合</t>
         </is>
@@ -4327,25 +3712,25 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>AI 对话</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Pi</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Inflection 出品的温和陪伴型对话助手,侧重自然交流</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>AI对话,陪伴</t>
         </is>
@@ -4363,13 +3748,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT2" display="https://baike.baidu.com/item/%E8%B0%B7%E6%AD%8C%E6%90%9C%E7%B4%A2%E5%BC%95%E6%93%8E" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT3" tooltip="https://baike.baidu.com/item/%E5%BF%85%E5%BA%94%20Bing" display="https://baike.baidu.com/item/%E5%BF%85%E5%BA%94%20Bing" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT4" display="https://baike.baidu.com/item/%E7%99%BE%E5%BA%A6%E6%90%9C%E7%B4%A2" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" tooltip="http://202.106.125.196" display="http://202.106.125.196" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT20" display="https://www.cppcc.gov.cn/" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" tooltip="https://sousuo.www.gov.cn/zcwjk/" display="https://sousuo.www.gov.cn/zcwjk/" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="BT21" display="https://www.cppcc.gov.cn/" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" tooltip="http://202.106.125.196" display="http://202.106.125.196" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" tooltip="https://sousuo.www.gov.cn/zcwjk/" display="https://sousuo.www.gov.cn/zcwjk/" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
